--- a/common/shared_components.xlsx
+++ b/common/shared_components.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikin\Documents\KybStudie\Vortex\vortex-nautilus-PCBs\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikin\Documents\KybStudie\Vortex\vortex-newtype-drone-PCBs\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFC5D43-4B6A-4A79-9898-8A275D404A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163E3FDF-1A3E-47BC-824B-9EF168138BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Type</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Projects</t>
   </si>
   <si>
-    <t>acoustics-power</t>
-  </si>
-  <si>
     <t>eFuse</t>
   </si>
   <si>
@@ -117,7 +114,16 @@
     <t>Side-Switch</t>
   </si>
   <si>
-    <t>acoustics-power, acoustics-filters</t>
+    <t>CAN-tranceiver</t>
+  </si>
+  <si>
+    <t>TCAN332G</t>
+  </si>
+  <si>
+    <t>Telemetry sensor</t>
+  </si>
+  <si>
+    <t>BME280</t>
   </si>
 </sst>
 </file>
@@ -436,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -452,7 +458,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -461,7 +467,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -469,109 +475,118 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
       <c r="D12">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="1"/>
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
